--- a/Outputs/Recycling_Plot_Data/Repeal/09_Demand_vs_Availability_2050_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/09_Demand_vs_Availability_2050_data_Repeal.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0.123058963367663</v>
+        <v>0.1229290630534933</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>0.728324675891862</v>
+        <v>0.727660346567341</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>1.599590718786036</v>
+        <v>1.59809110687942</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.1683011867572524</v>
+        <v>0.1681411064452723</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.08177448546973075</v>
+        <v>0.08168893435559561</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.7642474325089704</v>
+        <v>0.7634457545737866</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.0005376909499028626</v>
+        <v>0.0005385135781926651</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>0.007718969560005822</v>
+        <v>0.007718969392560806</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>0.002579143548942578</v>
+        <v>0.002583092677246966</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.0370503282092829</v>
+        <v>0.037050327798062</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.005496527054368564</v>
+        <v>0.005504950427440381</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.0005256698718016964</v>
+        <v>0.0005264746051166541</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.00755020370166796</v>
+        <v>0.007550203598297404</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.0003310821139036258</v>
+        <v>0.0003315883049661696</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0.004750328130206267</v>
+        <v>0.004750327985702297</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>0.003094192090663521</v>
+        <v>0.003098928251134248</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>0.04443692730908914</v>
+        <v>0.04443692662142314</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>0.0005681413377861311</v>
+        <v>0.0005689342646325644</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0.00816645747541505</v>
+        <v>0.008165343089678676</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>0.00271631455851595</v>
+        <v>0.002720127024920437</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>0.03904616561472531</v>
+        <v>0.03904114190827641</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.005801057410179811</v>
+        <v>0.005809196572652952</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>0.08339263358537834</v>
+        <v>0.08338185559515589</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.000554540955991941</v>
+        <v>0.0005553184638575877</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>0.007971257219357937</v>
+        <v>0.007970220101801458</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>0.0003510634906422901</v>
+        <v>0.0003515549728840578</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>0.005045983694225778</v>
+        <v>0.005045317288023076</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>0.003278934557442027</v>
+        <v>0.003283525811724015</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.04713272257842927</v>
+        <v>0.04712650397549614</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>0.004451425692190737</v>
+        <v>0.004449951882716519</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>0.0639496705505516</v>
+        <v>0.06383067757569379</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0.02501253434161779</v>
+        <v>0.02501275054300521</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0.3594638998578888</v>
+        <v>0.3589170043383372</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.05180066178706062</v>
+        <v>0.05179840387379495</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.7446562415169339</v>
+        <v>0.7434844006134063</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="G50">
-        <v>0.00487104452863141</v>
+        <v>0.004870666503492017</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>0.06999772512776006</v>
+        <v>0.06988520083695245</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.002767948627708944</v>
+        <v>0.002767418276148339</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.03975465927722312</v>
+        <v>0.03968622818014016</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.02581164622949086</v>
+        <v>0.0258042557949369</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="G55">
-        <v>0.3708830510399039</v>
+        <v>0.3702095236076033</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
